--- a/out/LSTM-Mamba1_metrics.xlsx
+++ b/out/LSTM-Mamba1_metrics.xlsx
@@ -472,16 +472,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001107765012420714</v>
+        <v>0.001107765082269907</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03328302502632141</v>
+        <v>0.03328302130103111</v>
       </c>
       <c r="C2" t="n">
         <v>0.02352975867688656</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.005291640758514404</v>
+        <v>-0.005291712284088135</v>
       </c>
       <c r="E2" t="n">
         <v>0.5154666666666667</v>
